--- a/src/ExcelsiorOpenXml.Tests/LinkTests.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/LinkTests.Null.verified.xlsx
@@ -137,6 +137,7 @@
   <autoFilter ref="A1:F2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="DeterministicId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="DeterministicId2"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/src/ExcelsiorOpenXml.Tests/LinkTests.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/LinkTests.Null.verified.xlsx
@@ -116,8 +116,6 @@
           <r>
             <rPr>
               <b/>
-              <u/>
-              <color rgb="0563C1"/>
             </rPr>
             <t xml:space="preserve">● </t>
           </r>

--- a/src/ExcelsiorOpenXml.Tests/LinkTests.Null.verified.xlsx
+++ b/src/ExcelsiorOpenXml.Tests/LinkTests.Null.verified.xlsx
@@ -132,7 +132,7 @@
       <c r="F2" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F2"/>
+  <autoFilter ref="A1:C2"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="DeterministicId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="DeterministicId2"/>
